--- a/inst/extdata/region/2026-08-14/wb_projects_gov_sar.xlsx
+++ b/inst/extdata/region/2026-08-14/wb_projects_gov_sar.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="72">
   <si>
     <t xml:space="preserve">proj_id</t>
   </si>
@@ -190,9 +190,6 @@
   </si>
   <si>
     <t xml:space="preserve">Public Sector Reform PASA for Bangladesh and Bhutan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8B</t>
   </si>
   <si>
     <t xml:space="preserve">Analytical</t>
@@ -1028,7 +1025,7 @@
         <v>25</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>59</v>
+        <v>26</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>27</v>
@@ -1040,20 +1037,20 @@
         <v>45513</v>
       </c>
       <c r="I2" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="J2" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="K2" s="2" t="s">
         <v>61</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>62</v>
       </c>
       <c r="L2" s="2"/>
       <c r="M2" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="N2" s="2" t="s">
         <v>63</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>64</v>
       </c>
       <c r="O2" s="2"/>
       <c r="P2" s="2"/>
@@ -1078,22 +1075,22 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>66</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>67</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E3" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>68</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>69</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>2026</v>
@@ -1102,20 +1099,20 @@
         <v>45929</v>
       </c>
       <c r="I3" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="J3" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J3" s="2" t="s">
-        <v>71</v>
-      </c>
       <c r="K3" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="L3" s="2"/>
       <c r="M3" s="2" t="s">
         <v>43</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" s="2"/>
@@ -1150,7 +1147,7 @@
         <v>25</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>40</v>
@@ -1162,20 +1159,20 @@
         <v>45513</v>
       </c>
       <c r="I4" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="J4" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="K4" s="2" t="s">
         <v>61</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>62</v>
       </c>
       <c r="L4" s="2"/>
       <c r="M4" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="N4" s="2" t="s">
         <v>63</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>64</v>
       </c>
       <c r="O4" s="2"/>
       <c r="P4" s="2"/>
